--- a/exp/jack/Data/UK_Data/hotmaps_num_buildings_GB.xlsx
+++ b/exp/jack/Data/UK_Data/hotmaps_num_buildings_GB.xlsx
@@ -76,7 +76,7 @@
     <t>Post 2010</t>
   </si>
   <si>
-    <t>Number of dwellings/units [Mil.]</t>
+    <t>Number of buildings [Mil.]</t>
   </si>
   <si>
     <t>1850-1944</t>
@@ -504,7 +504,7 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>7.117023429422105</v>
+        <v>4.29</v>
       </c>
       <c r="G2">
         <v>1850</v>
@@ -513,7 +513,7 @@
         <v>1944</v>
       </c>
       <c r="I2">
-        <v>0.07491603609918004</v>
+        <v>0.04515789473684211</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -536,7 +536,7 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>5.042448594150702</v>
+        <v>3.12</v>
       </c>
       <c r="G3">
         <v>1945</v>
@@ -545,7 +545,7 @@
         <v>1969</v>
       </c>
       <c r="I3">
-        <v>0.2016979437660281</v>
+        <v>0.1248</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
@@ -568,7 +568,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>1.910040669815751</v>
+        <v>1.36</v>
       </c>
       <c r="G4">
         <v>1970</v>
@@ -577,7 +577,7 @@
         <v>1979</v>
       </c>
       <c r="I4">
-        <v>0.1910040669815751</v>
+        <v>0.136</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
@@ -600,7 +600,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>1.382744239650282</v>
+        <v>1.06</v>
       </c>
       <c r="G5">
         <v>1980</v>
@@ -609,7 +609,7 @@
         <v>1989</v>
       </c>
       <c r="I5">
-        <v>0.1382744239650283</v>
+        <v>0.106</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
@@ -632,7 +632,7 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>1.368008351980379</v>
+        <v>1.05</v>
       </c>
       <c r="G6">
         <v>1990</v>
@@ -641,7 +641,7 @@
         <v>1999</v>
       </c>
       <c r="I6">
-        <v>0.1368008351980379</v>
+        <v>0.105</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -664,7 +664,7 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>3.987522190943282</v>
+        <v>2.52</v>
       </c>
       <c r="G7">
         <v>2000</v>
@@ -673,7 +673,7 @@
         <v>2009</v>
       </c>
       <c r="I7">
-        <v>0.3987522190943282</v>
+        <v>0.252</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -696,7 +696,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>3.088733993674984</v>
+        <v>2.02</v>
       </c>
       <c r="G8">
         <v>2010</v>
@@ -705,7 +705,7 @@
         <v>2022</v>
       </c>
       <c r="I8">
-        <v>0.2375949225903834</v>
+        <v>0.1553846153846154</v>
       </c>
       <c r="J8" t="s">
         <v>27</v>
@@ -728,7 +728,7 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>1.600165012666743</v>
+        <v>0.7</v>
       </c>
       <c r="G9">
         <v>1850</v>
@@ -737,7 +737,7 @@
         <v>1944</v>
       </c>
       <c r="I9">
-        <v>0.01684384223859729</v>
+        <v>0.007368421052631579</v>
       </c>
       <c r="J9" t="s">
         <v>21</v>
@@ -760,7 +760,7 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>0.5446009643986406</v>
+        <v>0.25</v>
       </c>
       <c r="G10">
         <v>1945</v>
@@ -769,7 +769,7 @@
         <v>1969</v>
       </c>
       <c r="I10">
-        <v>0.02178403857594562</v>
+        <v>0.01</v>
       </c>
       <c r="J10" t="s">
         <v>22</v>
@@ -792,7 +792,7 @@
         <v>20</v>
       </c>
       <c r="F11">
-        <v>0.5386123336900746</v>
+        <v>0.15</v>
       </c>
       <c r="G11">
         <v>1970</v>
@@ -801,7 +801,7 @@
         <v>1979</v>
       </c>
       <c r="I11">
-        <v>0.05386123336900746</v>
+        <v>0.015</v>
       </c>
       <c r="J11" t="s">
         <v>23</v>
@@ -824,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>0.3500673787961266</v>
+        <v>0.08</v>
       </c>
       <c r="G12">
         <v>1980</v>
@@ -833,7 +833,7 @@
         <v>1989</v>
       </c>
       <c r="I12">
-        <v>0.03500673787961266</v>
+        <v>0.008</v>
       </c>
       <c r="J12" t="s">
         <v>24</v>
@@ -856,7 +856,7 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>0.3242301163755778</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G13">
         <v>1990</v>
@@ -865,7 +865,7 @@
         <v>1999</v>
       </c>
       <c r="I13">
-        <v>0.03242301163755778</v>
+        <v>0.007000000000000001</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
@@ -888,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <v>0.7091369097616763</v>
+        <v>0.3</v>
       </c>
       <c r="G14">
         <v>2000</v>
@@ -897,7 +897,7 @@
         <v>2009</v>
       </c>
       <c r="I14">
-        <v>0.07091369097616763</v>
+        <v>0.03</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
@@ -920,7 +920,7 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>0.4066658146736709</v>
+        <v>0.2</v>
       </c>
       <c r="G15">
         <v>2010</v>
@@ -929,7 +929,7 @@
         <v>2022</v>
       </c>
       <c r="I15">
-        <v>0.03128198574412853</v>
+        <v>0.01538461538461539</v>
       </c>
       <c r="J15" t="s">
         <v>27</v>
@@ -952,7 +952,7 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>0.5966428924364383</v>
+        <v>0.14</v>
       </c>
       <c r="G16">
         <v>1850</v>
@@ -961,7 +961,7 @@
         <v>1944</v>
       </c>
       <c r="I16">
-        <v>0.006280451499330929</v>
+        <v>0.001473684210526316</v>
       </c>
       <c r="J16" t="s">
         <v>21</v>
@@ -984,7 +984,7 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>0.4042220988200464</v>
+        <v>0.1</v>
       </c>
       <c r="G17">
         <v>1945</v>
@@ -993,7 +993,7 @@
         <v>1969</v>
       </c>
       <c r="I17">
-        <v>0.01616888395280186</v>
+        <v>0.004</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -1016,7 +1016,7 @@
         <v>20</v>
       </c>
       <c r="F18">
-        <v>0.1807924866640345</v>
+        <v>0.04</v>
       </c>
       <c r="G18">
         <v>1970</v>
@@ -1025,7 +1025,7 @@
         <v>1979</v>
       </c>
       <c r="I18">
-        <v>0.01807924866640345</v>
+        <v>0.004</v>
       </c>
       <c r="J18" t="s">
         <v>23</v>
@@ -1048,7 +1048,7 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>0.1605813817230321</v>
+        <v>0.03</v>
       </c>
       <c r="G19">
         <v>1980</v>
@@ -1057,7 +1057,7 @@
         <v>1989</v>
       </c>
       <c r="I19">
-        <v>0.01605813817230321</v>
+        <v>0.003</v>
       </c>
       <c r="J19" t="s">
         <v>24</v>
@@ -1080,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>0.1107457804986428</v>
+        <v>0.02</v>
       </c>
       <c r="G20">
         <v>1990</v>
@@ -1089,7 +1089,7 @@
         <v>1999</v>
       </c>
       <c r="I20">
-        <v>0.01107457804986428</v>
+        <v>0.002</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
@@ -1112,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>0.3494029374732182</v>
+        <v>0.08</v>
       </c>
       <c r="G21">
         <v>2000</v>
@@ -1121,7 +1121,7 @@
         <v>2009</v>
       </c>
       <c r="I21">
-        <v>0.03494029374732182</v>
+        <v>0.008</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
@@ -1144,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="F22">
-        <v>0.216180470229022</v>
+        <v>0.05</v>
       </c>
       <c r="G22">
         <v>2010</v>
@@ -1153,7 +1153,7 @@
         <v>2022</v>
       </c>
       <c r="I22">
-        <v>0.016629266940694</v>
+        <v>0.003846153846153846</v>
       </c>
       <c r="J22" t="s">
         <v>27</v>
